--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">2345879</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F9">
-        <v>743</v>
+        <v>383</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">2357538</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>266</v>
+        <v>2003</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">2358512</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>1182</v>
+        <v>6827</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">240183</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F12">
-        <v>401</v>
+        <v>333</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">240368</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>1627</v>
+        <v>1165</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">242151, 242152</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>886</v>
+        <v>4039</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">247529, 247530, 247531</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>757</v>
+        <v>4978</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">247939</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>463</v>
+        <v>2643</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">501029, 501030, 2356545</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>743</v>
+        <v>687</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345879</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>383</v>
+        <v>1223</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346905</t>
+          <t xml:space="preserve">5318748</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>540</v>
+        <v>374</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356104</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F20">
-        <v>424</v>
+        <v>6822</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356104</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F21">
-        <v>1512</v>
+        <v>1738</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357538</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F22">
-        <v>2003</v>
+        <v>2666</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357851</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F23">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358512</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F24">
-        <v>6827</v>
+        <v>480</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">501029, 501030, 2356545</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F25">
-        <v>687</v>
+        <v>273</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F26">
-        <v>1223</v>
+        <v>3100</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318748</t>
+          <t xml:space="preserve">5323877</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F27">
-        <v>374</v>
+        <v>685</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">5323888, 100648966</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F28">
-        <v>6822</v>
+        <v>352</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>1738</v>
+        <v>1400</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">717838, 5325131</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F30">
-        <v>2666</v>
+        <v>362</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">717840, 5323992</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F31">
-        <v>867</v>
+        <v>1313</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">717848, 5323877</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F32">
-        <v>480</v>
+        <v>378</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">717859, 2344006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">717864, 2352874</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>3100</v>
+        <v>379</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323877</t>
+          <t xml:space="preserve">717866, 2344288</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323888, 100648966</t>
+          <t xml:space="preserve">717872, 5325403</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>352</v>
+        <v>480</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">717877, 2347235</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>1400</v>
+        <v>2147</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325389</t>
+          <t xml:space="preserve">717886, 7849361</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>430</v>
+        <v>1027</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">717838, 5325131</t>
+          <t xml:space="preserve">717904, 5324737</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>362</v>
+        <v>7191</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">717840, 5323992</t>
+          <t xml:space="preserve">9178082</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F40">
-        <v>1313</v>
+        <v>683</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,30 +2031,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">717841, 5323890</t>
+          <t xml:space="preserve">2347134</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>692</v>
+        <v>256</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026359</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">717848, 5323877</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F42">
-        <v>378</v>
+        <v>743</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2131,30 +2131,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">717859, 2344006</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F43">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2181,30 +2181,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">717864, 2352874</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F44">
-        <v>379</v>
+        <v>1182</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">717866, 2344288</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F45">
-        <v>713</v>
+        <v>401</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2281,30 +2281,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">717872, 5325403</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F46">
-        <v>480</v>
+        <v>1627</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">717877, 2347235</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F47">
-        <v>2147</v>
+        <v>886</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2381,30 +2381,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">717881, 5325389</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F48">
-        <v>1642</v>
+        <v>757</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2431,30 +2431,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">717886, 7849361</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F49">
-        <v>1027</v>
+        <v>463</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2481,30 +2481,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">717904, 5324737</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F50">
-        <v>7191</v>
+        <v>743</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">9178042</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>616</v>
+        <v>730</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026970</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2581,30 +2581,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">5321202</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>607</v>
+        <v>261</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200042486</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-12-07</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2631,30 +2631,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178082</t>
+          <t xml:space="preserve">2346163</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>683</v>
+        <v>378</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200043779</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347134</t>
+          <t xml:space="preserve">717841, 5323890</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F54">
-        <v>256</v>
+        <v>692</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026359</t>
+          <t xml:space="preserve">200053651</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-06</t>
+          <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178042</t>
+          <t xml:space="preserve">2356104</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F55">
-        <v>730</v>
+        <v>424</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026970</t>
+          <t xml:space="preserve">311074461</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352592</t>
+          <t xml:space="preserve">2356104</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F56">
-        <v>860</v>
+        <v>1512</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028527</t>
+          <t xml:space="preserve">311074461</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-25</t>
+          <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">2356585</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,26 +2840,26 @@
         </is>
       </c>
       <c r="F57">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028509</t>
+          <t xml:space="preserve">311275070</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-25</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2881,35 +2881,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">240183</t>
+          <t xml:space="preserve">2357851</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F58">
-        <v>333</v>
+        <v>874</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041218</t>
+          <t xml:space="preserve">311275077</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-17</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2931,35 +2931,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321202</t>
+          <t xml:space="preserve">2358407</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F59">
-        <v>261</v>
+        <v>1817</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042486</t>
+          <t xml:space="preserve">311275076</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-07</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2981,35 +2981,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346163</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F60">
-        <v>378</v>
+        <v>982</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043779</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-03</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356585</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>380</v>
+        <v>3192</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275070</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-26</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358407</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F62">
-        <v>1817</v>
+        <v>2628</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275076</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-26</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F63">
-        <v>982</v>
+        <v>1824</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F64">
-        <v>3192</v>
+        <v>370</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3236,11 +3236,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F65">
-        <v>2628</v>
+        <v>457</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F66">
-        <v>1824</v>
+        <v>2368</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291129</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F67">
-        <v>370</v>
+        <v>1228</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291125</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F68">
-        <v>457</v>
+        <v>4128</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291125</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3436,15 +3436,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F69">
-        <v>2368</v>
+        <v>3580</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291129</t>
+          <t xml:space="preserve">311291126</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>1228</v>
+        <v>1592</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291125</t>
+          <t xml:space="preserve">311291333</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71">
-        <v>4128</v>
+        <v>320</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291125</t>
+          <t xml:space="preserve">311291335</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F72">
-        <v>3580</v>
+        <v>2211</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291126</t>
+          <t xml:space="preserve">311291333</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">5325787</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>1592</v>
+        <v>5072</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291333</t>
+          <t xml:space="preserve">311292191</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-01-11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291335</t>
+          <t xml:space="preserve">311306326</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F75">
-        <v>2211</v>
+        <v>252</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291333</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325787</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F76">
-        <v>5072</v>
+        <v>616</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292191</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-11</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3836,11 +3836,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3886,15 +3886,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306332</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3936,15 +3936,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F79">
-        <v>417</v>
+        <v>607</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306326</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">5320965</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F80">
-        <v>331</v>
+        <v>480</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306335</t>
+          <t xml:space="preserve">311306929</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-04</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5320965</t>
+          <t xml:space="preserve">2356550</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>480</v>
+        <v>3255</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306929</t>
+          <t xml:space="preserve">311309850</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356550</t>
+          <t xml:space="preserve">5323874</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>3255</v>
+        <v>6181</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309850</t>
+          <t xml:space="preserve">311312001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-05-03</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4136,11 +4136,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>6181</v>
+        <v>5081</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323874</t>
+          <t xml:space="preserve">7167452</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>5081</v>
+        <v>1528</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312001</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-03</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">247529, 247530, 247531</t>
+          <t xml:space="preserve">7167452</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F85">
-        <v>4978</v>
+        <v>312</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319267</t>
+          <t xml:space="preserve">311319698</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-08</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4286,15 +4286,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F86">
-        <v>1528</v>
+        <v>1158</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311319699</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4336,11 +4336,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F87">
-        <v>312</v>
+        <v>720</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4386,11 +4386,11 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F88">
-        <v>1158</v>
+        <v>568</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4436,15 +4436,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F89">
-        <v>720</v>
+        <v>769</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319698</t>
+          <t xml:space="preserve">311319701</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4486,15 +4486,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>568</v>
+        <v>453</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319699</t>
+          <t xml:space="preserve">311319702</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4536,15 +4536,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91">
-        <v>769</v>
+        <v>942</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319701</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4586,15 +4586,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F92">
-        <v>453</v>
+        <v>1378</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319702</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4636,11 +4636,11 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F93">
-        <v>942</v>
+        <v>904</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4686,15 +4686,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F94">
-        <v>1378</v>
+        <v>448</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311319699</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7167452</t>
+          <t xml:space="preserve">5324564</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>904</v>
+        <v>396</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311320667</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-06-14</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7167452</t>
+          <t xml:space="preserve">5323880</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>448</v>
+        <v>512</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319699</t>
+          <t xml:space="preserve">311329809</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324564</t>
+          <t xml:space="preserve">5323880</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F97">
-        <v>396</v>
+        <v>5396</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320667</t>
+          <t xml:space="preserve">311329809</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-14</t>
+          <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4886,11 +4886,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F98">
-        <v>512</v>
+        <v>381</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323880</t>
+          <t xml:space="preserve">8317731</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>5396</v>
+        <v>14580</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329809</t>
+          <t xml:space="preserve">311331067</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-10</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323880</t>
+          <t xml:space="preserve">8317731</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F100">
-        <v>381</v>
+        <v>264</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329809</t>
+          <t xml:space="preserve">311331068</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-10</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8317731</t>
+          <t xml:space="preserve">2345383</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F101">
-        <v>14580</v>
+        <v>481</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331067</t>
+          <t xml:space="preserve">311332405</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8317731</t>
+          <t xml:space="preserve">2345383</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>264</v>
+        <v>606</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331068</t>
+          <t xml:space="preserve">311335910</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5136,20 +5136,20 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F103">
-        <v>481</v>
+        <v>702</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332405</t>
+          <t xml:space="preserve">311335910</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-24</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345383</t>
+          <t xml:space="preserve">2345686</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,11 +5190,11 @@
         </is>
       </c>
       <c r="F104">
-        <v>606</v>
+        <v>1868</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335910</t>
+          <t xml:space="preserve">311335940</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5231,20 +5231,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345383</t>
+          <t xml:space="preserve">2345686</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F105">
-        <v>702</v>
+        <v>380</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335910</t>
+          <t xml:space="preserve">311335940</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345686</t>
+          <t xml:space="preserve">2349770</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="F106">
-        <v>1868</v>
+        <v>330</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335940</t>
+          <t xml:space="preserve">311335985</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5331,20 +5331,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345686</t>
+          <t xml:space="preserve">2349770</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F107">
-        <v>380</v>
+        <v>317</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335940</t>
+          <t xml:space="preserve">311335985</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5386,11 +5386,11 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F108">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5431,20 +5431,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349770</t>
+          <t xml:space="preserve">5325785</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>317</v>
+        <v>401</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335985</t>
+          <t xml:space="preserve">311335988</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349770</t>
+          <t xml:space="preserve">5325785</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F110">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335985</t>
+          <t xml:space="preserve">311335988</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F111">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325785</t>
+          <t xml:space="preserve">2352592</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>368</v>
+        <v>860</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335988</t>
+          <t xml:space="preserve">311338049</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325785</t>
+          <t xml:space="preserve">2352592</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>422</v>
+        <v>1252</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335988</t>
+          <t xml:space="preserve">311338049</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5686,15 +5686,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F114">
-        <v>1252</v>
+        <v>451</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338051</t>
+          <t xml:space="preserve">311338047</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5731,20 +5731,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352592</t>
+          <t xml:space="preserve">2352622</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F115">
-        <v>451</v>
+        <v>577</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338047</t>
+          <t xml:space="preserve">311338056</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5781,20 +5781,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352622</t>
+          <t xml:space="preserve">2352874</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F116">
-        <v>577</v>
+        <v>406</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338056</t>
+          <t xml:space="preserve">311338050</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352874</t>
+          <t xml:space="preserve">5323050</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>406</v>
+        <v>6162</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338050</t>
+          <t xml:space="preserve">311340215</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323050</t>
+          <t xml:space="preserve">5324915</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="F118">
-        <v>6162</v>
+        <v>2362</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340215</t>
+          <t xml:space="preserve">311340188</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F119">
-        <v>2362</v>
+        <v>1500</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5986,11 +5986,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F120">
-        <v>1500</v>
+        <v>4601</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6036,11 +6036,11 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F121">
-        <v>4601</v>
+        <v>1062</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6086,15 +6086,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F122">
-        <v>1062</v>
+        <v>493</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340188</t>
+          <t xml:space="preserve">311340187</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324915</t>
+          <t xml:space="preserve">2347138</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>493</v>
+        <v>1545</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340187</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6186,15 +6186,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F124">
-        <v>1545</v>
+        <v>297</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6236,15 +6236,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F125">
-        <v>297</v>
+        <v>561</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347687</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6286,11 +6286,11 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F126">
-        <v>561</v>
+        <v>1897</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6336,15 +6336,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F127">
-        <v>1897</v>
+        <v>685</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6386,15 +6386,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F128">
-        <v>685</v>
+        <v>1045</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347687</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6436,11 +6436,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F129">
-        <v>1045</v>
+        <v>925</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6486,11 +6486,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F130">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6536,11 +6536,11 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F131">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -6586,11 +6586,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F132">
-        <v>945</v>
+        <v>905</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347138</t>
+          <t xml:space="preserve">2356354</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F133">
-        <v>905</v>
+        <v>4304</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311350280</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-20</t>
+          <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6686,15 +6686,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F134">
-        <v>4304</v>
+        <v>264</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350280</t>
+          <t xml:space="preserve">311350287</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6736,15 +6736,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F135">
-        <v>264</v>
+        <v>913</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350287</t>
+          <t xml:space="preserve">311350291</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356354</t>
+          <t xml:space="preserve">2340899</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F136">
-        <v>913</v>
+        <v>1222</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350291</t>
+          <t xml:space="preserve">311359055</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-06</t>
+          <t xml:space="preserve">2029-02-11</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6836,11 +6836,11 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F137">
-        <v>1222</v>
+        <v>416</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340899</t>
+          <t xml:space="preserve">5318942</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F138">
-        <v>416</v>
+        <v>330</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359055</t>
+          <t xml:space="preserve">311363467</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-11</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318942</t>
+          <t xml:space="preserve">5319832</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="F139">
-        <v>330</v>
+        <v>659</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363467</t>
+          <t xml:space="preserve">311363463</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319832</t>
+          <t xml:space="preserve">1309837</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F140">
-        <v>659</v>
+        <v>303</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363463</t>
+          <t xml:space="preserve">311366646</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-03-25</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,20 +7031,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309837</t>
+          <t xml:space="preserve">2346492</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>303</v>
+        <v>480</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366646</t>
+          <t xml:space="preserve">311366648</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346492</t>
+          <t xml:space="preserve">5324009</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>480</v>
+        <v>1350</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366649</t>
+          <t xml:space="preserve">311373442</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-25</t>
+          <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7432769</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F143">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367097</t>
+          <t xml:space="preserve">311373445</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324009</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F144">
-        <v>1350</v>
+        <v>703</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373442</t>
+          <t xml:space="preserve">311373444</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">5323054</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145">
-        <v>300</v>
+        <v>7508</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373445</t>
+          <t xml:space="preserve">311374178</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-29</t>
+          <t xml:space="preserve">2029-05-01</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">2344534</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>703</v>
+        <v>302</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373444</t>
+          <t xml:space="preserve">311376005</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-29</t>
+          <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323054</t>
+          <t xml:space="preserve">2352621</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>7508</v>
+        <v>310</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374178</t>
+          <t xml:space="preserve">311376000</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-01</t>
+          <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2344534</t>
+          <t xml:space="preserve">2347133</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F148">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376005</t>
+          <t xml:space="preserve">311376587</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-09</t>
+          <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352621</t>
+          <t xml:space="preserve">5322519</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>310</v>
+        <v>423</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376000</t>
+          <t xml:space="preserve">311376589</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-09</t>
+          <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347133</t>
+          <t xml:space="preserve">5318912</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>256</v>
+        <v>1068</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376587</t>
+          <t xml:space="preserve">311379834</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-13</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322519</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c r="F151">
-        <v>423</v>
+        <v>680</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376589</t>
+          <t xml:space="preserve">311379842</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-13</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318912</t>
+          <t xml:space="preserve">5318749</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>1068</v>
+        <v>348</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379834</t>
+          <t xml:space="preserve">311382562</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">5319307</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F153">
-        <v>680</v>
+        <v>528</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379842</t>
+          <t xml:space="preserve">311382518</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318749</t>
+          <t xml:space="preserve">5319387</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,11 +7690,11 @@
         </is>
       </c>
       <c r="F154">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382562</t>
+          <t xml:space="preserve">311382550</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319307</t>
+          <t xml:space="preserve">100054031</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F155">
-        <v>528</v>
+        <v>420</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382518</t>
+          <t xml:space="preserve">311382765</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-14</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319387</t>
+          <t xml:space="preserve">5319307</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F156">
-        <v>308</v>
+        <v>1031</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382550</t>
+          <t xml:space="preserve">311382770</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-14</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054031</t>
+          <t xml:space="preserve">5318651</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>420</v>
+        <v>836</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382765</t>
+          <t xml:space="preserve">311386295</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319307</t>
+          <t xml:space="preserve">5319374</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>1031</v>
+        <v>436</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382770</t>
+          <t xml:space="preserve">311386294</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318651</t>
+          <t xml:space="preserve">8138301</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>836</v>
+        <v>571</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386295</t>
+          <t xml:space="preserve">311386898</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-03</t>
+          <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319374</t>
+          <t xml:space="preserve">8138301</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F160">
-        <v>436</v>
+        <v>2912</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386294</t>
+          <t xml:space="preserve">311386898</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-03</t>
+          <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8138301</t>
+          <t xml:space="preserve">2345264</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F161">
-        <v>571</v>
+        <v>335</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386898</t>
+          <t xml:space="preserve">311387209</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-04</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8138301</t>
+          <t xml:space="preserve">2345503</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F162">
-        <v>2912</v>
+        <v>810</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386898</t>
+          <t xml:space="preserve">311387207</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-04</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345264</t>
+          <t xml:space="preserve">7793099</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F163">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387209</t>
+          <t xml:space="preserve">311391486</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345503</t>
+          <t xml:space="preserve">2358278</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F164">
-        <v>810</v>
+        <v>712</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387207</t>
+          <t xml:space="preserve">311397099</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321259</t>
+          <t xml:space="preserve">9177966</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>564</v>
+        <v>402</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387211</t>
+          <t xml:space="preserve">311397085</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7793099</t>
+          <t xml:space="preserve">9834784</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>451</v>
+        <v>940</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391486</t>
+          <t xml:space="preserve">311397089</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358278</t>
+          <t xml:space="preserve">2346169</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>712</v>
+        <v>498</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397099</t>
+          <t xml:space="preserve">311397885</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177966</t>
+          <t xml:space="preserve">8014114</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>402</v>
+        <v>1066</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397085</t>
+          <t xml:space="preserve">311397811</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9834784</t>
+          <t xml:space="preserve">2341294</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>940</v>
+        <v>344</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397089</t>
+          <t xml:space="preserve">311399300</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-19</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346169</t>
+          <t xml:space="preserve">5325901</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397885</t>
+          <t xml:space="preserve">311400170</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-11</t>
+          <t xml:space="preserve">2029-09-24</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8014114</t>
+          <t xml:space="preserve">5319950</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="F171">
-        <v>1066</v>
+        <v>706</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397811</t>
+          <t xml:space="preserve">311400300</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-11</t>
+          <t xml:space="preserve">2029-09-25</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341294</t>
+          <t xml:space="preserve">5319374</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>344</v>
+        <v>870</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311399300</t>
+          <t xml:space="preserve">311402388</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-19</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325901</t>
+          <t xml:space="preserve">5325900</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="F173">
-        <v>368</v>
+        <v>482</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400170</t>
+          <t xml:space="preserve">311402390</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-24</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319950</t>
+          <t xml:space="preserve">5325900</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F174">
-        <v>706</v>
+        <v>324</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400300</t>
+          <t xml:space="preserve">311402390</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-25</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8374376</t>
+          <t xml:space="preserve">8961322</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>7542</v>
+        <v>3598</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401335</t>
+          <t xml:space="preserve">311403409</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-01</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8374376</t>
+          <t xml:space="preserve">8961322</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F176">
-        <v>908</v>
+        <v>262</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311401335</t>
+          <t xml:space="preserve">311403409</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-01</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319374</t>
+          <t xml:space="preserve">10131361</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F177">
-        <v>870</v>
+        <v>731</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402388</t>
+          <t xml:space="preserve">311405352</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2029-10-24</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325900</t>
+          <t xml:space="preserve">2345879</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F178">
-        <v>482</v>
+        <v>683</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402390</t>
+          <t xml:space="preserve">311464629</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325900</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402390</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961322</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F180">
-        <v>3598</v>
+        <v>590</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403409</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961322</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F181">
-        <v>262</v>
+        <v>1440</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403409</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131361</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F182">
-        <v>731</v>
+        <v>900</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405352</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-24</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F183">
-        <v>1440</v>
+        <v>6331</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410840</t>
+          <t xml:space="preserve">311526504</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-26</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">9178076</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F184">
-        <v>900</v>
+        <v>1075</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410840</t>
+          <t xml:space="preserve">311552078</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-26</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345879</t>
+          <t xml:space="preserve">5325389</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>683</v>
+        <v>430</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464629</t>
+          <t xml:space="preserve">311557655</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">717881, 5325389</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F186">
-        <v>590</v>
+        <v>1642</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464682</t>
+          <t xml:space="preserve">311557655</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178076</t>
+          <t xml:space="preserve">9177863</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>1075</v>
+        <v>388</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311524787</t>
+          <t xml:space="preserve">311573247</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-02</t>
+          <t xml:space="preserve">2032-01-19</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">5325188</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F188">
-        <v>6331</v>
+        <v>999</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526504</t>
+          <t xml:space="preserve">311582594</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9436,20 +9436,20 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F189">
-        <v>388</v>
+        <v>730</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573247</t>
+          <t xml:space="preserve">311582596</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-19</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325188</t>
+          <t xml:space="preserve">5322601</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9490,16 +9490,16 @@
         </is>
       </c>
       <c r="F190">
-        <v>999</v>
+        <v>1280</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582594</t>
+          <t xml:space="preserve">311582923</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177863</t>
+          <t xml:space="preserve">5322601</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F191">
-        <v>730</v>
+        <v>990</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582596</t>
+          <t xml:space="preserve">311582923</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322601</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F192">
-        <v>1280</v>
+        <v>327</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582923</t>
+          <t xml:space="preserve">311599683</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322601</t>
+          <t xml:space="preserve">10131363</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F193">
-        <v>990</v>
+        <v>19102</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582923</t>
+          <t xml:space="preserve">311663591</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2033-03-01</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">717853, 5325389</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F194">
-        <v>327</v>
+        <v>491</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599683</t>
+          <t xml:space="preserve">311688976</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2033-06-20</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131363</t>
+          <t xml:space="preserve">5321259</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9740,16 +9740,16 @@
         </is>
       </c>
       <c r="F195">
-        <v>19102</v>
+        <v>564</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663591</t>
+          <t xml:space="preserve">311728689</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-01</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">247939</t>
+          <t xml:space="preserve">2346708</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,16 +9790,16 @@
         </is>
       </c>
       <c r="F196">
-        <v>2643</v>
+        <v>3050</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686295</t>
+          <t xml:space="preserve">311729442</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">717853, 5325389</t>
+          <t xml:space="preserve">2346905</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F197">
-        <v>491</v>
+        <v>540</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688976</t>
+          <t xml:space="preserve">311729474</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-20</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">242151, 242152</t>
+          <t xml:space="preserve">8374376</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="F198">
-        <v>4039</v>
+        <v>7542</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715696</t>
+          <t xml:space="preserve">311729462</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-17</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,20 +9931,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346708</t>
+          <t xml:space="preserve">8374376</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F199">
-        <v>3050</v>
+        <v>908</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729442</t>
+          <t xml:space="preserve">311729462</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319448</t>
+          <t xml:space="preserve">7432769</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10040,16 +10040,16 @@
         </is>
       </c>
       <c r="F201">
-        <v>1460</v>
+        <v>750</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730427</t>
+          <t xml:space="preserve">311729784</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2033-12-18</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347161</t>
+          <t xml:space="preserve">5319448</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10090,16 +10090,16 @@
         </is>
       </c>
       <c r="F202">
-        <v>421</v>
+        <v>1460</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730882</t>
+          <t xml:space="preserve">311730427</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-21</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">2347161</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F203">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731030</t>
+          <t xml:space="preserve">311730882</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10186,20 +10186,20 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F204">
-        <v>267</v>
+        <v>400</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736452</t>
+          <t xml:space="preserve">311731030</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323538</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F205">
-        <v>440</v>
+        <v>267</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743328</t>
+          <t xml:space="preserve">311736452</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">240368</t>
+          <t xml:space="preserve">5323538</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>1165</v>
+        <v>440</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743669</t>
+          <t xml:space="preserve">311743328</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">

--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Gudmands Vej 16C</t>
+          <t xml:space="preserve">Blokhusvej 3A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122215</t>
+          <t xml:space="preserve">100758442</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>1142</v>
+        <v>271</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 65</t>
+          <t xml:space="preserve">Blokhusvej 3F</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100318741, 100318742</t>
+          <t xml:space="preserve">100758442</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H3">
-        <v>2353</v>
+        <v>1577</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 3A</t>
+          <t xml:space="preserve">Blokhusvej 5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H4">
-        <v>271</v>
+        <v>519</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 5</t>
+          <t xml:space="preserve">Carl Bødker Nielsens Vej 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100758442</t>
+          <t xml:space="preserve">717877, 2347235</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>519</v>
+        <v>2147</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 3F</t>
+          <t xml:space="preserve">Erik Gudmands Vej 16C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100758442</t>
+          <t xml:space="preserve">100122215</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H6">
-        <v>1577</v>
+        <v>1142</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvdalsvej 15</t>
+          <t xml:space="preserve">Gl Hellebækvej 65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100831159</t>
+          <t xml:space="preserve">100318741, 100318742</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H7">
-        <v>605</v>
+        <v>2353</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 9</t>
+          <t xml:space="preserve">Gl Hellebækvej 71C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340886</t>
+          <t xml:space="preserve">5323888, 100648966</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H8">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gørlundevej 4A</t>
+          <t xml:space="preserve">Gl Hellebækvej 73</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345879</t>
+          <t xml:space="preserve">717840, 5323992</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H9">
-        <v>383</v>
+        <v>1313</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 5</t>
+          <t xml:space="preserve">Gørlundevej 4A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357538</t>
+          <t xml:space="preserve">2345879</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H10">
-        <v>2003</v>
+        <v>383</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,17 +631,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 19</t>
+          <t xml:space="preserve">Hallandsvej 59</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358512</t>
+          <t xml:space="preserve">717866, 2344288</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H11">
-        <v>6827</v>
+        <v>713</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Anchers Vej 27</t>
+          <t xml:space="preserve">Hymersvej 14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">240183</t>
+          <t xml:space="preserve">5323877</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H12">
-        <v>333</v>
+        <v>685</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkeldamsvej 10</t>
+          <t xml:space="preserve">Hymersvej 19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">240368</t>
+          <t xml:space="preserve">717848, 5323877</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H13">
-        <v>1165</v>
+        <v>378</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylfesvej 17A</t>
+          <t xml:space="preserve">Idrætsvej 19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">242151, 242152</t>
+          <t xml:space="preserve">2358512</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>4039</v>
+        <v>6827</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 1A</t>
+          <t xml:space="preserve">Idrætsvej 5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">247529, 247530, 247531</t>
+          <t xml:space="preserve">2357538</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="H15">
-        <v>4978</v>
+        <v>2003</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundtoldvej 2</t>
+          <t xml:space="preserve">Klostermosevej 106A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">247939</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>2643</v>
+        <v>1400</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 3A</t>
+          <t xml:space="preserve">Klostermosevej 9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">501029, 501030, 2356545</t>
+          <t xml:space="preserve">2340886</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>687</v>
+        <v>396</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienlyst Alle 2</t>
+          <t xml:space="preserve">Lundegade 17A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">5318748</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>1223</v>
+        <v>374</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegade 17A</t>
+          <t xml:space="preserve">Løvdalsvej 15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318748</t>
+          <t xml:space="preserve">100831159</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>374</v>
+        <v>605</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Kronborgvej 10</t>
+          <t xml:space="preserve">Marienlyst Alle 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H20">
-        <v>6822</v>
+        <v>1223</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Kronborgvej 8</t>
+          <t xml:space="preserve">Nordhavnsvej 2A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">9178082</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H21">
-        <v>1738</v>
+        <v>683</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Kronborgvej 2</t>
+          <t xml:space="preserve">Nordre Strandvej 148A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">717859, 2344006</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>2666</v>
+        <v>261</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Anna Gade 3</t>
+          <t xml:space="preserve">Ny Kronborgvej 1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">717904, 5324737</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>867</v>
+        <v>7191</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Anna Gade 5E</t>
+          <t xml:space="preserve">Ny Kronborgvej 10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H24">
-        <v>480</v>
+        <v>6822</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Anna Gade 5C</t>
+          <t xml:space="preserve">Ny Kronborgvej 2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H25">
-        <v>273</v>
+        <v>2666</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stengade 59</t>
+          <t xml:space="preserve">Ny Kronborgvej 8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H26">
-        <v>3100</v>
+        <v>1738</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hymersvej 14</t>
+          <t xml:space="preserve">Nørremarken 3A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323877</t>
+          <t xml:space="preserve">501029, 501030, 2356545</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H27">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 71C</t>
+          <t xml:space="preserve">Præstegårdsvej 19B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3080</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323888, 100648966</t>
+          <t xml:space="preserve">717864, 2352874</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 106A</t>
+          <t xml:space="preserve">Sct Anna Gade 3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H29">
-        <v>1400</v>
+        <v>867</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sperlings Allé 43</t>
+          <t xml:space="preserve">Sct Anna Gade 5C</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">717838, 5325131</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H30">
-        <v>362</v>
+        <v>273</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 73</t>
+          <t xml:space="preserve">Sct Anna Gade 5E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">717840, 5323992</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H31">
-        <v>1313</v>
+        <v>480</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hymersvej 19</t>
+          <t xml:space="preserve">Sperlings Allé 43</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">717848, 5323877</t>
+          <t xml:space="preserve">717838, 5325131</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H32">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 148A</t>
+          <t xml:space="preserve">Stengade 59</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">717859, 2344006</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>261</v>
+        <v>3100</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 19B</t>
+          <t xml:space="preserve">Strandpromenaden 6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">717864, 2352874</t>
+          <t xml:space="preserve">717872, 5325403</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>379</v>
+        <v>480</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hallandsvej 59</t>
+          <t xml:space="preserve">Vestermarken 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">717866, 2344288</t>
+          <t xml:space="preserve">717886, 7849361</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="H35">
-        <v>713</v>
+        <v>1027</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,17 +2131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandpromenaden 6</t>
+          <t xml:space="preserve">Søren Kannes Vej 3A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">717872, 5325403</t>
+          <t xml:space="preserve">2347134</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="H36">
-        <v>480</v>
+        <v>256</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026359</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-06</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2191,40 +2191,40 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Bødker Nielsens Vej 3</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">717877, 2347235</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H37">
-        <v>2147</v>
+        <v>743</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2251,40 +2251,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarken 1</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">717886, 7849361</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H38">
-        <v>1027</v>
+        <v>266</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2311,40 +2311,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Kronborgvej 1</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">717904, 5324737</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H39">
-        <v>7191</v>
+        <v>1182</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2371,40 +2371,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordhavnsvej 2A</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178082</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H40">
-        <v>683</v>
+        <v>401</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Kannes Vej 3A</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347134</t>
+          <t xml:space="preserve">2345371</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>256</v>
+        <v>1627</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026359</t>
+          <t xml:space="preserve">200026422</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-06</t>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2506,11 +2506,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H42">
-        <v>743</v>
+        <v>886</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2566,11 +2566,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H43">
-        <v>266</v>
+        <v>757</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H44">
-        <v>1182</v>
+        <v>463</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2686,11 +2686,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H45">
-        <v>401</v>
+        <v>743</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Færgevej 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">9178042</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>1627</v>
+        <v>730</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026422</t>
+          <t xml:space="preserve">200026970</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,35 +2791,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Anna Anchers Vej 27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">240183</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H47">
-        <v>886</v>
+        <v>333</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026422</t>
+          <t xml:space="preserve">200041218</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2020-11-17</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Rønnebær Alle 170</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">5321202</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>757</v>
+        <v>261</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026422</t>
+          <t xml:space="preserve">200042486</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2020-12-07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Vingen 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,25 +2921,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">2346163</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026422</t>
+          <t xml:space="preserve">200043779</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2021-01-03</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Gl Hellebækvej 71A</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345371</t>
+          <t xml:space="preserve">717841, 5323890</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H50">
-        <v>743</v>
+        <v>692</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026422</t>
+          <t xml:space="preserve">200053651</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 1</t>
+          <t xml:space="preserve">Gymnasievej 5A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178042</t>
+          <t xml:space="preserve">2356104</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H51">
-        <v>730</v>
+        <v>1512</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026970</t>
+          <t xml:space="preserve">311074461</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebær Alle 170</t>
+          <t xml:space="preserve">Gymnasievej 5B</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321202</t>
+          <t xml:space="preserve">2356104</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H52">
-        <v>261</v>
+        <v>424</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042486</t>
+          <t xml:space="preserve">311074461</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-07</t>
+          <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vingen 2</t>
+          <t xml:space="preserve">Fredensvej 5A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346163</t>
+          <t xml:space="preserve">2356585</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,26 +3170,26 @@
         </is>
       </c>
       <c r="H53">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043779</t>
+          <t xml:space="preserve">311275070</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-03</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3211,45 +3211,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 71A</t>
+          <t xml:space="preserve">Idrætsvej 19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">717841, 5323890</t>
+          <t xml:space="preserve">2357851</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H54">
-        <v>692</v>
+        <v>874</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053651</t>
+          <t xml:space="preserve">311275077</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-07</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 5B</t>
+          <t xml:space="preserve">Svend Poulsens Vej 154</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,35 +3281,35 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356104</t>
+          <t xml:space="preserve">2358407</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H55">
-        <v>424</v>
+        <v>1817</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311074461</t>
+          <t xml:space="preserve">311275076</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-19</t>
+          <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 5A</t>
+          <t xml:space="preserve">Grydemosevej 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,35 +3341,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356104</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H56">
-        <v>1512</v>
+        <v>982</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311074461</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-19</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 5A</t>
+          <t xml:space="preserve">Grydemosevej 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356585</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H57">
-        <v>380</v>
+        <v>3192</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275070</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-26</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 19</t>
+          <t xml:space="preserve">Grydemosevej 2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357851</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H58">
-        <v>874</v>
+        <v>2628</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275077</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-26</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Poulsens Vej 154</t>
+          <t xml:space="preserve">Grydemosevej 2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,25 +3521,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358407</t>
+          <t xml:space="preserve">9178024</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H59">
-        <v>1817</v>
+        <v>1824</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275076</t>
+          <t xml:space="preserve">311288375</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-26</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H60">
-        <v>982</v>
+        <v>457</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grydemosevej 2</t>
+          <t xml:space="preserve">Grydemosevej 4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3646,11 +3646,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H61">
-        <v>3192</v>
+        <v>370</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grydemosevej 2</t>
+          <t xml:space="preserve">Allegade 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H62">
-        <v>2628</v>
+        <v>2368</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291129</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grydemosevej 2</t>
+          <t xml:space="preserve">Allegade 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H63">
-        <v>1824</v>
+        <v>1228</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291125</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grydemosevej 4</t>
+          <t xml:space="preserve">Allegade 2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H64">
-        <v>370</v>
+        <v>4128</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291125</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grydemosevej 2</t>
+          <t xml:space="preserve">Ny Kronborgvej 12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178024</t>
+          <t xml:space="preserve">5318753</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H65">
-        <v>457</v>
+        <v>3580</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288375</t>
+          <t xml:space="preserve">311291126</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 2</t>
+          <t xml:space="preserve">Ritavej 7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>2368</v>
+        <v>320</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291129</t>
+          <t xml:space="preserve">311291335</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,35 +3991,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 2</t>
+          <t xml:space="preserve">Stokholmsvej 10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>1228</v>
+        <v>1592</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291125</t>
+          <t xml:space="preserve">311291333</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 2</t>
+          <t xml:space="preserve">Stokholmsvej 10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">2341727</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H68">
-        <v>4128</v>
+        <v>2211</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291125</t>
+          <t xml:space="preserve">311291333</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Kronborgvej 12</t>
+          <t xml:space="preserve">Nørrevej 95</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318753</t>
+          <t xml:space="preserve">5325787</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>3580</v>
+        <v>5072</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291126</t>
+          <t xml:space="preserve">311292191</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-11</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stokholmsvej 10</t>
+          <t xml:space="preserve">Agnetevej 9A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>1592</v>
+        <v>450</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291333</t>
+          <t xml:space="preserve">311306326</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ritavej 7</t>
+          <t xml:space="preserve">Agnetevej 9A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,25 +4241,25 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H71">
-        <v>320</v>
+        <v>616</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291335</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stokholmsvej 10</t>
+          <t xml:space="preserve">Agnetevej 9A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341727</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>2211</v>
+        <v>331</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291333</t>
+          <t xml:space="preserve">311306335</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevej 95</t>
+          <t xml:space="preserve">Agnetevej 9B</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325787</t>
+          <t xml:space="preserve">9178017</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H73">
-        <v>5072</v>
+        <v>417</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292191</t>
+          <t xml:space="preserve">311306326</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-11</t>
+          <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 9A</t>
+          <t xml:space="preserve">Agnetevej 9G</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4426,11 +4426,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H74">
-        <v>450</v>
+        <v>607</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306332</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 9A</t>
+          <t xml:space="preserve">Stubbedamsvej 10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">5320965</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>616</v>
+        <v>480</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306929</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-04</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 9B</t>
+          <t xml:space="preserve">Kløvermarken 12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,25 +4601,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">2356550</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>417</v>
+        <v>3255</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311309850</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-04</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 9A</t>
+          <t xml:space="preserve">Rasmus Knudsens Vej 50</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">5323874</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>331</v>
+        <v>6181</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311312001</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-04</t>
+          <t xml:space="preserve">2028-05-03</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,35 +4711,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 9G</t>
+          <t xml:space="preserve">Rasmus Knudsens Vej 52</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178017</t>
+          <t xml:space="preserve">5323874</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H79">
-        <v>607</v>
+        <v>5081</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311312001</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-04</t>
+          <t xml:space="preserve">2028-05-03</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbedamsvej 10</t>
+          <t xml:space="preserve">Kronborgvej 1A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5320965</t>
+          <t xml:space="preserve">247529, 247530, 247531</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>480</v>
+        <v>4978</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306929</t>
+          <t xml:space="preserve">311319267</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,35 +4831,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 12</t>
+          <t xml:space="preserve">Abildgaardsvej 45</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356550</t>
+          <t xml:space="preserve">7167452</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H81">
-        <v>3255</v>
+        <v>453</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309850</t>
+          <t xml:space="preserve">311319702</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmus Knudsens Vej 50</t>
+          <t xml:space="preserve">Blichersvej 121</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323874</t>
+          <t xml:space="preserve">7167452</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>6181</v>
+        <v>1528</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312001</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-03</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmus Knudsens Vej 52</t>
+          <t xml:space="preserve">Blichersvej 121</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,25 +4961,25 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323874</t>
+          <t xml:space="preserve">7167452</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H83">
-        <v>5081</v>
+        <v>312</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312001</t>
+          <t xml:space="preserve">311319698</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-03</t>
+          <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5026,15 +5026,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H84">
-        <v>1528</v>
+        <v>1158</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311319699</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5086,11 +5086,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H85">
-        <v>312</v>
+        <v>720</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5146,11 +5146,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H86">
-        <v>1158</v>
+        <v>568</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5206,15 +5206,15 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H87">
-        <v>720</v>
+        <v>769</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319698</t>
+          <t xml:space="preserve">311319701</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5266,15 +5266,15 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H88">
-        <v>568</v>
+        <v>942</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319699</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5326,15 +5326,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H89">
-        <v>769</v>
+        <v>1378</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319701</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildgaardsvej 45</t>
+          <t xml:space="preserve">Blichersvej 121</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5386,15 +5386,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H90">
-        <v>453</v>
+        <v>904</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319702</t>
+          <t xml:space="preserve">311319697</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5446,15 +5446,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H91">
-        <v>942</v>
+        <v>448</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311319699</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blichersvej 121</t>
+          <t xml:space="preserve">Krbg Ladegårds Vej 114</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,25 +5501,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7167452</t>
+          <t xml:space="preserve">5324564</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>1378</v>
+        <v>396</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311320667</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-06-14</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blichersvej 121</t>
+          <t xml:space="preserve">Gl Hellebækvej 61E</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7167452</t>
+          <t xml:space="preserve">5323880</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>904</v>
+        <v>512</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319697</t>
+          <t xml:space="preserve">311329809</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blichersvej 121</t>
+          <t xml:space="preserve">Gl Hellebækvej 63</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,25 +5621,25 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7167452</t>
+          <t xml:space="preserve">5323880</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H94">
-        <v>448</v>
+        <v>5396</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319699</t>
+          <t xml:space="preserve">311329809</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-11</t>
+          <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krbg Ladegårds Vej 114</t>
+          <t xml:space="preserve">Gl Hellebækvej 67</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324564</t>
+          <t xml:space="preserve">5323880</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H95">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320667</t>
+          <t xml:space="preserve">311329809</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-14</t>
+          <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 61E</t>
+          <t xml:space="preserve">Smakkevej 2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323880</t>
+          <t xml:space="preserve">8317731</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>512</v>
+        <v>14580</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329809</t>
+          <t xml:space="preserve">311331067</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-10</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 63</t>
+          <t xml:space="preserve">Smakkevej 2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323880</t>
+          <t xml:space="preserve">8317731</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H97">
-        <v>5396</v>
+        <v>264</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329809</t>
+          <t xml:space="preserve">311331068</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-10</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hellebækvej 67</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323880</t>
+          <t xml:space="preserve">2345383</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>381</v>
+        <v>481</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329809</t>
+          <t xml:space="preserve">311332405</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-10</t>
+          <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smakkevej 2</t>
+          <t xml:space="preserve">Hellebækvej 44</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8317731</t>
+          <t xml:space="preserve">2345686</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>14580</v>
+        <v>1868</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331067</t>
+          <t xml:space="preserve">311335940</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smakkevej 2</t>
+          <t xml:space="preserve">Hellebækvej 44</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8317731</t>
+          <t xml:space="preserve">2345686</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331068</t>
+          <t xml:space="preserve">311335940</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Klyveren 2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345383</t>
+          <t xml:space="preserve">5325785</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332405</t>
+          <t xml:space="preserve">311335988</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-24</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,30 +6091,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Klyveren 4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345383</t>
+          <t xml:space="preserve">5325785</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H102">
-        <v>606</v>
+        <v>368</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335910</t>
+          <t xml:space="preserve">311335988</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,30 +6151,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåningevej 11</t>
+          <t xml:space="preserve">Klyveren 6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345383</t>
+          <t xml:space="preserve">5325785</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H103">
-        <v>702</v>
+        <v>422</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335910</t>
+          <t xml:space="preserve">311335988</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellebækvej 44</t>
+          <t xml:space="preserve">Nordre Strandvej 450</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345686</t>
+          <t xml:space="preserve">2349770</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,11 +6230,11 @@
         </is>
       </c>
       <c r="H104">
-        <v>1868</v>
+        <v>330</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335940</t>
+          <t xml:space="preserve">311335985</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,30 +6271,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellebækvej 44</t>
+          <t xml:space="preserve">Nordre Strandvej 450</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345686</t>
+          <t xml:space="preserve">2349770</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H105">
-        <v>380</v>
+        <v>317</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335940</t>
+          <t xml:space="preserve">311335985</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H106">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,30 +6391,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 450</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349770</t>
+          <t xml:space="preserve">2345383</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>317</v>
+        <v>606</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335985</t>
+          <t xml:space="preserve">311335910</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,30 +6451,30 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 450</t>
+          <t xml:space="preserve">Skåningevej 11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349770</t>
+          <t xml:space="preserve">2345383</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H108">
-        <v>317</v>
+        <v>702</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335985</t>
+          <t xml:space="preserve">311335910</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klyveren 2</t>
+          <t xml:space="preserve">Præstegårdsvej 19C</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3080</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325785</t>
+          <t xml:space="preserve">2352874</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335988</t>
+          <t xml:space="preserve">311338050</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klyveren 4</t>
+          <t xml:space="preserve">Præstegårdsvej 21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3080</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325785</t>
+          <t xml:space="preserve">2352592</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>368</v>
+        <v>860</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335988</t>
+          <t xml:space="preserve">311338049</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klyveren 6</t>
+          <t xml:space="preserve">Præstegårdsvej 21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3080</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325785</t>
+          <t xml:space="preserve">2352592</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>422</v>
+        <v>1252</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335988</t>
+          <t xml:space="preserve">311338051</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6706,15 +6706,15 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H112">
-        <v>860</v>
+        <v>451</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338049</t>
+          <t xml:space="preserve">311338047</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6761,20 +6761,20 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352592</t>
+          <t xml:space="preserve">2352622</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H113">
-        <v>1252</v>
+        <v>577</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338049</t>
+          <t xml:space="preserve">311338056</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 21</t>
+          <t xml:space="preserve">Borgm.P.Christensens Vej 14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352592</t>
+          <t xml:space="preserve">5323050</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>451</v>
+        <v>6162</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338047</t>
+          <t xml:space="preserve">311340215</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 21</t>
+          <t xml:space="preserve">Gefionsvej 93</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352622</t>
+          <t xml:space="preserve">5324915</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>577</v>
+        <v>2362</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338056</t>
+          <t xml:space="preserve">311340188</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 19C</t>
+          <t xml:space="preserve">Gefionsvej 93</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352874</t>
+          <t xml:space="preserve">5324915</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>406</v>
+        <v>4601</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338050</t>
+          <t xml:space="preserve">311340188</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgm.P.Christensens Vej 14</t>
+          <t xml:space="preserve">Gefionsvej 93</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,20 +7001,20 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323050</t>
+          <t xml:space="preserve">5324915</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H117">
-        <v>6162</v>
+        <v>1062</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340215</t>
+          <t xml:space="preserve">311340188</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 93</t>
+          <t xml:space="preserve">Skolealleen 2A</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7066,11 +7066,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H118">
-        <v>2362</v>
+        <v>1500</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolealleen 2A</t>
+          <t xml:space="preserve">Skolealleen 2B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7126,15 +7126,15 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H119">
-        <v>1500</v>
+        <v>493</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340188</t>
+          <t xml:space="preserve">311340187</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 93</t>
+          <t xml:space="preserve">Søren Kannes Vej 6A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324915</t>
+          <t xml:space="preserve">2347138</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>4601</v>
+        <v>1545</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340188</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 93</t>
+          <t xml:space="preserve">Søren Kannes Vej 6A</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324915</t>
+          <t xml:space="preserve">2347138</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H121">
-        <v>1062</v>
+        <v>297</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340188</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolealleen 2B</t>
+          <t xml:space="preserve">Søren Kannes Vej 6A</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324915</t>
+          <t xml:space="preserve">2347138</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H122">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340187</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-08</t>
+          <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7366,15 +7366,15 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H123">
-        <v>1545</v>
+        <v>1897</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7426,15 +7426,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H124">
-        <v>297</v>
+        <v>685</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7486,15 +7486,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H125">
-        <v>561</v>
+        <v>1045</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7546,15 +7546,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H126">
-        <v>1897</v>
+        <v>925</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7606,15 +7606,15 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H127">
-        <v>685</v>
+        <v>935</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7666,15 +7666,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H128">
-        <v>1045</v>
+        <v>945</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7726,15 +7726,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H129">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,35 +7771,35 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Kannes Vej 6A</t>
+          <t xml:space="preserve">Nørremarken 15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347138</t>
+          <t xml:space="preserve">2356354</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H130">
-        <v>935</v>
+        <v>264</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311350287</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-20</t>
+          <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,35 +7831,35 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Kannes Vej 6A</t>
+          <t xml:space="preserve">Rugmarken 1A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347138</t>
+          <t xml:space="preserve">2356354</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>945</v>
+        <v>4304</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311350280</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-20</t>
+          <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Kannes Vej 6A</t>
+          <t xml:space="preserve">Rugmarken 1A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347138</t>
+          <t xml:space="preserve">2356354</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,16 +7910,16 @@
         </is>
       </c>
       <c r="H132">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311350291</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-20</t>
+          <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 1A</t>
+          <t xml:space="preserve">Klostermosevej 9</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356354</t>
+          <t xml:space="preserve">2340899</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>4304</v>
+        <v>1222</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350280</t>
+          <t xml:space="preserve">311359055</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-06</t>
+          <t xml:space="preserve">2029-02-11</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,35 +8011,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 15</t>
+          <t xml:space="preserve">Klostermosevej 9</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356354</t>
+          <t xml:space="preserve">2340899</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H134">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350287</t>
+          <t xml:space="preserve">311359055</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-06</t>
+          <t xml:space="preserve">2029-02-11</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 1A</t>
+          <t xml:space="preserve">Nygade 6C</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356354</t>
+          <t xml:space="preserve">5318942</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>913</v>
+        <v>330</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350291</t>
+          <t xml:space="preserve">311363467</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-06</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 9</t>
+          <t xml:space="preserve">Rosenkildevej 32</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340899</t>
+          <t xml:space="preserve">5319832</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>1222</v>
+        <v>659</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359055</t>
+          <t xml:space="preserve">311363463</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-11</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 9</t>
+          <t xml:space="preserve">Bøghsvej 2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340899</t>
+          <t xml:space="preserve">1309837</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H137">
-        <v>416</v>
+        <v>303</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359055</t>
+          <t xml:space="preserve">311366646</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-11</t>
+          <t xml:space="preserve">2029-03-25</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 6C</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 40</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318942</t>
+          <t xml:space="preserve">2346492</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,16 +8270,16 @@
         </is>
       </c>
       <c r="H138">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363467</t>
+          <t xml:space="preserve">311366649</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-03-25</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildevej 32</t>
+          <t xml:space="preserve">Klostermosevej 106C</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,25 +8321,25 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319832</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>659</v>
+        <v>703</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363463</t>
+          <t xml:space="preserve">311373444</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,35 +8371,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøghsvej 2</t>
+          <t xml:space="preserve">Klostermosevej 106D</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309837</t>
+          <t xml:space="preserve">5324205</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H140">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366646</t>
+          <t xml:space="preserve">311373445</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-25</t>
+          <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,17 +8431,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 40</t>
+          <t xml:space="preserve">Løvdalsvej 9</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346492</t>
+          <t xml:space="preserve">5324009</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8450,16 +8450,16 @@
         </is>
       </c>
       <c r="H141">
-        <v>480</v>
+        <v>1350</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366648</t>
+          <t xml:space="preserve">311373442</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-25</t>
+          <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvdalsvej 9</t>
+          <t xml:space="preserve">Birkedalsvej 27</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324009</t>
+          <t xml:space="preserve">5323054</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="H142">
-        <v>1350</v>
+        <v>7508</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373442</t>
+          <t xml:space="preserve">311374178</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-29</t>
+          <t xml:space="preserve">2029-05-01</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,35 +8551,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 106D</t>
+          <t xml:space="preserve">Hornbækvej 465</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3080</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">2352621</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373445</t>
+          <t xml:space="preserve">311376000</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-29</t>
+          <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 106C</t>
+          <t xml:space="preserve">Knudemosevej 13C</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324205</t>
+          <t xml:space="preserve">2344534</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>703</v>
+        <v>302</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373444</t>
+          <t xml:space="preserve">311376005</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-29</t>
+          <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkedalsvej 27</t>
+          <t xml:space="preserve">Søndre Strandvej 29A</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323054</t>
+          <t xml:space="preserve">5322519</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>7508</v>
+        <v>423</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374178</t>
+          <t xml:space="preserve">311376589</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-01</t>
+          <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudemosevej 13C</t>
+          <t xml:space="preserve">Søren Kannes Vej 5A</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2344534</t>
+          <t xml:space="preserve">2347133</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H146">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376005</t>
+          <t xml:space="preserve">311376587</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-09</t>
+          <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornbækvej 465</t>
+          <t xml:space="preserve">Sct Anna Gade 5A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352621</t>
+          <t xml:space="preserve">5318912</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>310</v>
+        <v>1068</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376000</t>
+          <t xml:space="preserve">311379834</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-09</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Kannes Vej 5A</t>
+          <t xml:space="preserve">Sct Anna Gade 5B</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347133</t>
+          <t xml:space="preserve">5318915</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H148">
-        <v>256</v>
+        <v>680</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376587</t>
+          <t xml:space="preserve">311379842</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-13</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Strandvej 29A</t>
+          <t xml:space="preserve">Fiolgade 17D</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,25 +8921,25 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322519</t>
+          <t xml:space="preserve">5319307</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149">
-        <v>423</v>
+        <v>528</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376589</t>
+          <t xml:space="preserve">311382518</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-13</t>
+          <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Anna Gade 5A</t>
+          <t xml:space="preserve">Lundegade 15A</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318912</t>
+          <t xml:space="preserve">5318749</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>1068</v>
+        <v>348</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379834</t>
+          <t xml:space="preserve">311382562</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Anna Gade 5B</t>
+          <t xml:space="preserve">Rantzausvej 4</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318915</t>
+          <t xml:space="preserve">5319387</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H151">
-        <v>680</v>
+        <v>308</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379842</t>
+          <t xml:space="preserve">311382550</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundegade 15A</t>
+          <t xml:space="preserve">Fiolgade 15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,25 +9101,25 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318749</t>
+          <t xml:space="preserve">100054031</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H152">
-        <v>348</v>
+        <v>420</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382562</t>
+          <t xml:space="preserve">311382765</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-14</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiolgade 17D</t>
+          <t xml:space="preserve">Fiolgade 17B</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9166,20 +9166,20 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H153">
-        <v>528</v>
+        <v>1031</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382518</t>
+          <t xml:space="preserve">311382770</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-14</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rantzausvej 4</t>
+          <t xml:space="preserve">Allegade 25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319387</t>
+          <t xml:space="preserve">5318651</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,16 +9230,16 @@
         </is>
       </c>
       <c r="H154">
-        <v>308</v>
+        <v>836</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382550</t>
+          <t xml:space="preserve">311386295</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-14</t>
+          <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiolgade 15</t>
+          <t xml:space="preserve">Trækbanen 7</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054031</t>
+          <t xml:space="preserve">5319374</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382765</t>
+          <t xml:space="preserve">311386294</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,35 +9331,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiolgade 17B</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319307</t>
+          <t xml:space="preserve">8138301</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H156">
-        <v>1031</v>
+        <v>571</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382770</t>
+          <t xml:space="preserve">311386898</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,35 +9391,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 25</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318651</t>
+          <t xml:space="preserve">8138301</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H157">
-        <v>836</v>
+        <v>2912</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386295</t>
+          <t xml:space="preserve">311386898</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-03</t>
+          <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,35 +9451,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trækbanen 7</t>
+          <t xml:space="preserve">Jæmtlandsvej 1</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319374</t>
+          <t xml:space="preserve">2345503</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H158">
-        <v>436</v>
+        <v>810</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386294</t>
+          <t xml:space="preserve">311387207</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-03</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Jæmtlandsvej 4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,25 +9521,25 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8138301</t>
+          <t xml:space="preserve">2345264</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H159">
-        <v>571</v>
+        <v>335</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386898</t>
+          <t xml:space="preserve">311387209</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-04</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Gefionsvej 63</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8138301</t>
+          <t xml:space="preserve">7793099</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>2912</v>
+        <v>451</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311386898</t>
+          <t xml:space="preserve">311391486</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-04</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jæmtlandsvej 4</t>
+          <t xml:space="preserve">Egegårdsvej 3A</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345264</t>
+          <t xml:space="preserve">2358278</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H161">
-        <v>335</v>
+        <v>712</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387209</t>
+          <t xml:space="preserve">311397099</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,35 +9691,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jæmtlandsvej 1</t>
+          <t xml:space="preserve">Kongevejen 280</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345503</t>
+          <t xml:space="preserve">9834784</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H162">
-        <v>810</v>
+        <v>940</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387207</t>
+          <t xml:space="preserve">311397089</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gefionsvej 63</t>
+          <t xml:space="preserve">Reerstrupvej 2A</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7793099</t>
+          <t xml:space="preserve">9177966</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H163">
-        <v>451</v>
+        <v>402</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391486</t>
+          <t xml:space="preserve">311397085</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,17 +9811,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egegårdsvej 3A</t>
+          <t xml:space="preserve">H P Christensens Vej 24</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358278</t>
+          <t xml:space="preserve">8014114</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,16 +9830,16 @@
         </is>
       </c>
       <c r="H164">
-        <v>712</v>
+        <v>1066</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397099</t>
+          <t xml:space="preserve">311397811</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reerstrupvej 2A</t>
+          <t xml:space="preserve">Orøvej 11</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177966</t>
+          <t xml:space="preserve">2346169</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="H165">
-        <v>402</v>
+        <v>498</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397085</t>
+          <t xml:space="preserve">311397885</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 280</t>
+          <t xml:space="preserve">Strandvejen 167A</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9834784</t>
+          <t xml:space="preserve">2341294</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,16 +9950,16 @@
         </is>
       </c>
       <c r="H166">
-        <v>940</v>
+        <v>344</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397089</t>
+          <t xml:space="preserve">311399300</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-06</t>
+          <t xml:space="preserve">2029-09-19</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orøvej 11</t>
+          <t xml:space="preserve">Løntoften 4</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346169</t>
+          <t xml:space="preserve">5325901</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,16 +10010,16 @@
         </is>
       </c>
       <c r="H167">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397885</t>
+          <t xml:space="preserve">311400170</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-11</t>
+          <t xml:space="preserve">2029-09-24</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">H P Christensens Vej 24</t>
+          <t xml:space="preserve">Horsensvej 8A</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8014114</t>
+          <t xml:space="preserve">5319950</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="H168">
-        <v>1066</v>
+        <v>706</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311397811</t>
+          <t xml:space="preserve">311400300</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-11</t>
+          <t xml:space="preserve">2029-09-25</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,35 +10111,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 167A</t>
+          <t xml:space="preserve">Rosenkildestien 5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3060</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341294</t>
+          <t xml:space="preserve">5319374</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H169">
-        <v>344</v>
+        <v>870</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311399300</t>
+          <t xml:space="preserve">311402388</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-19</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løntoften 4</t>
+          <t xml:space="preserve">Smakkevej 3A</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325901</t>
+          <t xml:space="preserve">5325900</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H170">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400170</t>
+          <t xml:space="preserve">311402390</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-24</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 8A</t>
+          <t xml:space="preserve">Smakkevej 3B</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319950</t>
+          <t xml:space="preserve">5325900</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10250,16 +10250,16 @@
         </is>
       </c>
       <c r="H171">
-        <v>706</v>
+        <v>482</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311400300</t>
+          <t xml:space="preserve">311402390</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-25</t>
+          <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,35 +10291,35 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkildestien 5</t>
+          <t xml:space="preserve">Agnetevej 1</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3070</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319374</t>
+          <t xml:space="preserve">8961322</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H172">
-        <v>870</v>
+        <v>3598</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402388</t>
+          <t xml:space="preserve">311403409</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smakkevej 3B</t>
+          <t xml:space="preserve">Agnetevej 1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,25 +10361,25 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325900</t>
+          <t xml:space="preserve">8961322</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H173">
-        <v>482</v>
+        <v>262</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402390</t>
+          <t xml:space="preserve">311403409</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,35 +10411,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smakkevej 3A</t>
+          <t xml:space="preserve">Borgm.P.Christensens Vej 4A</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325900</t>
+          <t xml:space="preserve">10131361</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H174">
-        <v>324</v>
+        <v>731</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402390</t>
+          <t xml:space="preserve">311405352</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-07</t>
+          <t xml:space="preserve">2029-10-24</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,35 +10471,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 1</t>
+          <t xml:space="preserve">Gørlundevej 4B</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3140</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961322</t>
+          <t xml:space="preserve">2345879</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H175">
-        <v>3598</v>
+        <v>683</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403409</t>
+          <t xml:space="preserve">311464629</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,35 +10531,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agnetevej 1</t>
+          <t xml:space="preserve">Kongevejen 425A</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3070</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961322</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403409</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,35 +10591,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgm.P.Christensens Vej 4A</t>
+          <t xml:space="preserve">Kongevejen 425C</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131361</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H177">
-        <v>731</v>
+        <v>590</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405352</t>
+          <t xml:space="preserve">311464682</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-24</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gørlundevej 4B</t>
+          <t xml:space="preserve">Kongevejen 425C</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2345879</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178">
-        <v>683</v>
+        <v>1440</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464629</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 425A</t>
+          <t xml:space="preserve">Kongevejen 425C</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10726,11 +10726,11 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H179">
-        <v>290</v>
+        <v>900</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 425C</t>
+          <t xml:space="preserve">Marienlyst Alle 2</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H180">
-        <v>590</v>
+        <v>6331</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311526504</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,35 +10831,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 425C</t>
+          <t xml:space="preserve">Nordre Strandvej 14</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">9178076</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H181">
-        <v>1440</v>
+        <v>1075</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311552127</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,35 +10891,35 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 425C</t>
+          <t xml:space="preserve">Nordhavnsvej 13</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">5325389</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H182">
-        <v>900</v>
+        <v>430</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311557655</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienlyst Alle 2</t>
+          <t xml:space="preserve">Nordhavnsvej 1C</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10961,25 +10961,25 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">717881, 5325389</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H183">
-        <v>6331</v>
+        <v>1642</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526504</t>
+          <t xml:space="preserve">311557655</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-08</t>
+          <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 14</t>
+          <t xml:space="preserve">Hellebækvej 46</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,25 +11021,25 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178076</t>
+          <t xml:space="preserve">9177863</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>1075</v>
+        <v>388</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552127</t>
+          <t xml:space="preserve">311573247</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2032-01-19</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordhavnsvej 13</t>
+          <t xml:space="preserve">Hellebækvej 61</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325389</t>
+          <t xml:space="preserve">9177863</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H185">
-        <v>430</v>
+        <v>730</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557655</t>
+          <t xml:space="preserve">311582596</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-26</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordhavnsvej 1C</t>
+          <t xml:space="preserve">Nordre Strandvej 24</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">717881, 5325389</t>
+          <t xml:space="preserve">5325188</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H186">
-        <v>1642</v>
+        <v>999</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311557655</t>
+          <t xml:space="preserve">311582594</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-26</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellebækvej 46</t>
+          <t xml:space="preserve">Gl Banegårdsvej 35</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,25 +11201,25 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177863</t>
+          <t xml:space="preserve">5322601</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H187">
-        <v>388</v>
+        <v>990</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573247</t>
+          <t xml:space="preserve">311582923</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-19</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Strandvej 24</t>
+          <t xml:space="preserve">Gl Banegårdsvej 37</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5325188</t>
+          <t xml:space="preserve">5322601</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11270,16 +11270,16 @@
         </is>
       </c>
       <c r="H188">
-        <v>999</v>
+        <v>1280</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582594</t>
+          <t xml:space="preserve">311582923</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellebækvej 61</t>
+          <t xml:space="preserve">Marienlyst Alle 2</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,25 +11321,25 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177863</t>
+          <t xml:space="preserve">5318734</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H189">
-        <v>730</v>
+        <v>327</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582596</t>
+          <t xml:space="preserve">311599683</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Banegårdsvej 37</t>
+          <t xml:space="preserve">Birkedalsvej 35A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322601</t>
+          <t xml:space="preserve">10131363</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,16 +11390,16 @@
         </is>
       </c>
       <c r="H190">
-        <v>1280</v>
+        <v>19102</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582923</t>
+          <t xml:space="preserve">311663591</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2033-03-01</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Banegårdsvej 35</t>
+          <t xml:space="preserve">Sundtoldvej 2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,25 +11441,25 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5322601</t>
+          <t xml:space="preserve">247939</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H191">
-        <v>990</v>
+        <v>2643</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582923</t>
+          <t xml:space="preserve">311686295</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienlyst Alle 2</t>
+          <t xml:space="preserve">Nordhavnsvej 5</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11501,25 +11501,25 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318734</t>
+          <t xml:space="preserve">717853, 5325389</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H192">
-        <v>327</v>
+        <v>491</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599683</t>
+          <t xml:space="preserve">311688976</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2033-06-20</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,17 +11551,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkedalsvej 35A</t>
+          <t xml:space="preserve">Gylfesvej 17A</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3060</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">10131363</t>
+          <t xml:space="preserve">242151, 242152</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,16 +11570,16 @@
         </is>
       </c>
       <c r="H193">
-        <v>19102</v>
+        <v>4039</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311663591</t>
+          <t xml:space="preserve">311715696</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-01</t>
+          <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordhavnsvej 5</t>
+          <t xml:space="preserve">Gl Banegårdsvej 27</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11621,25 +11621,25 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">717853, 5325389</t>
+          <t xml:space="preserve">5321259</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H194">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688976</t>
+          <t xml:space="preserve">311728689</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-20</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Banegårdsvej 27</t>
+          <t xml:space="preserve">Egevænget 6</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321259</t>
+          <t xml:space="preserve">8374376</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11690,16 +11690,16 @@
         </is>
       </c>
       <c r="H195">
-        <v>564</v>
+        <v>7542</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728689</t>
+          <t xml:space="preserve">311729462</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,30 +11731,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegårdsvej 50A</t>
+          <t xml:space="preserve">Egevænget 6</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346708</t>
+          <t xml:space="preserve">8374376</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H196">
-        <v>3050</v>
+        <v>908</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729442</t>
+          <t xml:space="preserve">311729462</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sauntevej 4B</t>
+          <t xml:space="preserve">Holmegårdsvej 50A</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346905</t>
+          <t xml:space="preserve">2346708</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11810,11 +11810,11 @@
         </is>
       </c>
       <c r="H197">
-        <v>540</v>
+        <v>3050</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729474</t>
+          <t xml:space="preserve">311729442</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevænget 6</t>
+          <t xml:space="preserve">Sauntevej 4B</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8374376</t>
+          <t xml:space="preserve">2346905</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11870,11 +11870,11 @@
         </is>
       </c>
       <c r="H198">
-        <v>7542</v>
+        <v>540</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729462</t>
+          <t xml:space="preserve">311729474</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevænget 6</t>
+          <t xml:space="preserve">Krøyersvej 4</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11921,25 +11921,25 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8374376</t>
+          <t xml:space="preserve">7432769</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>908</v>
+        <v>750</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729462</t>
+          <t xml:space="preserve">311729784</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2033-12-18</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krøyersvej 4</t>
+          <t xml:space="preserve">Svingelport 6A</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7432769</t>
+          <t xml:space="preserve">5319448</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12050,16 +12050,16 @@
         </is>
       </c>
       <c r="H201">
-        <v>750</v>
+        <v>1460</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729784</t>
+          <t xml:space="preserve">311730427</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-18</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,17 +12091,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svingelport 6A</t>
+          <t xml:space="preserve">Per Bjørns Vej 20A</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3100</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319448</t>
+          <t xml:space="preserve">2347161</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -12110,16 +12110,16 @@
         </is>
       </c>
       <c r="H202">
-        <v>1460</v>
+        <v>421</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730427</t>
+          <t xml:space="preserve">311730882</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,35 +12151,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per Bjørns Vej 20A</t>
+          <t xml:space="preserve">Kongevejen 431A</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100</t>
+          <t xml:space="preserve">3490</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2347161</t>
+          <t xml:space="preserve">9178019</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H203">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730882</t>
+          <t xml:space="preserve">311731030</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-21</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 431A</t>
+          <t xml:space="preserve">Kongevejen 431C</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12226,20 +12226,20 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H204">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731030</t>
+          <t xml:space="preserve">311736452</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12271,35 +12271,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 431C</t>
+          <t xml:space="preserve">Løvdalsvej 8A</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3490</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9178019</t>
+          <t xml:space="preserve">5323538</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H205">
-        <v>267</v>
+        <v>440</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736452</t>
+          <t xml:space="preserve">311743328</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvdalsvej 8A</t>
+          <t xml:space="preserve">Vinkeldamsvej 10</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12341,25 +12341,25 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5323538</t>
+          <t xml:space="preserve">240368</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H206">
-        <v>440</v>
+        <v>1165</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743328</t>
+          <t xml:space="preserve">311743669</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">

--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306336</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306336</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552127</t>
+          <t xml:space="preserve">311552078</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">

--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -4194,7 +4194,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306326</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306336</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306335</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306326</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306336</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306332</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347687</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347687</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347686</t>
+          <t xml:space="preserve">311347688</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350287</t>
+          <t xml:space="preserve">311350294</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464676</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464676</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464676</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552078</t>
+          <t xml:space="preserve">311552127</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730427</t>
+          <t xml:space="preserve">311730523</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">

--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L222"/>
+  <dimension ref="A1:M222"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-06</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-17</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-07</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-03</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-07</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-09-19</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-26</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-11</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4194,20 +4539,25 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306326</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4254,20 +4604,25 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306336</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4314,20 +4669,25 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306335</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4374,20 +4734,25 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306326</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4434,20 +4799,25 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306336</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4494,20 +4864,25 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306329</t>
+          <t xml:space="preserve">311306336</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-04</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-03</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-03</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-11</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-14</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-10</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-24</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-08</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-20</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7854,20 +8504,25 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350280</t>
+          <t xml:space="preserve">311350294</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-06</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-11</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-11</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-25</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-25</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-29</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-01</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-09</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-13</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-14</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-03</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-04</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-06</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-11</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-19</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-24</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-25</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-07</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-24</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10614,20 +11494,25 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464682</t>
+          <t xml:space="preserve">311464679</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">NØRREGAARD, Rådgivende Ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-08</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-26</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-19</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">NØRREGAARD, Rådgivende Ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-01</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-20</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-18</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-18</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-16</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lantner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Varme og Fugtteknik  ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,21 +14424,26 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L222"/>
+  <autoFilter ref="A1:M222"/>
 </worksheet>
 </file>
--- a/public/exports/64502018.xlsx
+++ b/public/exports/64502018.xlsx
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306336</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306335</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306336</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306336</t>
+          <t xml:space="preserve">311306329</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311338051</t>
+          <t xml:space="preserve">311338049</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347687</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347688</t>
+          <t xml:space="preserve">311347686</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350294</t>
+          <t xml:space="preserve">311350287</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350294</t>
+          <t xml:space="preserve">311350280</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366649</t>
+          <t xml:space="preserve">311366648</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464679</t>
+          <t xml:space="preserve">311464676</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552127</t>
+          <t xml:space="preserve">311552078</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730523</t>
+          <t xml:space="preserve">311730427</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
